--- a/output/details/2026-06-01/preprocessed_data.xlsx
+++ b/output/details/2026-06-01/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46174</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1180870800835905</v>
+        <v>-0.1249104615263314</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1326231173078907</v>
+        <v>-0.1448781822558917</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1324472525748943</v>
+        <v>-0.1445963892421593</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1157886477288725</v>
+        <v>-0.001754580825433018</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001695682378978855</v>
+        <v>0.001690413588440026</v>
       </c>
       <c r="G2" t="n">
-        <v>1.995112084904346</v>
+        <v>2.547266440753056</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4295571033049012</v>
+        <v>-0.2659981378197638</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
